--- a/data/trans_orig/P57B2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57B2_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido feliz en 2023</t>
+          <t>Población según se ha sentido feliz en 2023 (tasa de respuesta: 99,61%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>253166</t>
+          <t>255176</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>315855</t>
+          <t>320033</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>176422</t>
+          <t>174788</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>221070</t>
+          <t>219323</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>441988</t>
+          <t>446271</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>523390</t>
+          <t>523631</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,42%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67271</t>
+          <t>64606</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128222</t>
+          <t>122164</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61609</t>
+          <t>63761</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>103789</t>
+          <t>105079</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141101</t>
+          <t>139732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>216473</t>
+          <t>212229</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29305</t>
+          <t>28865</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20227</t>
+          <t>21396</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50531</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32544</t>
+          <t>32042</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>72710</t>
+          <t>70228</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27144</t>
+          <t>24633</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,62 +1104,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2889</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>25889</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>6309</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>24433</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>208701</t>
+          <t>206499</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>262609</t>
+          <t>260696</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>147419</t>
+          <t>140680</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>284485</t>
+          <t>285865</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>372690</t>
+          <t>346860</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>524393</t>
+          <t>526809</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,34%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124994</t>
+          <t>126086</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>175077</t>
+          <t>176492</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>187373</t>
+          <t>186484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>350358</t>
+          <t>345197</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>331531</t>
+          <t>331559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>508580</t>
+          <t>525925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>56,25%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19234</t>
+          <t>20498</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48096</t>
+          <t>47726</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43042</t>
+          <t>42894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43849</t>
+          <t>42753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81587</t>
+          <t>80999</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>15173</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21614</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>279666</t>
+          <t>280077</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>328942</t>
+          <t>327588</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>274156</t>
+          <t>273877</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>310806</t>
+          <t>310814</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>568291</t>
+          <t>564822</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>631600</t>
+          <t>625996</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>146361</t>
+          <t>148094</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>190730</t>
+          <t>191222</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>173779</t>
+          <t>174197</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>209401</t>
+          <t>209440</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>328778</t>
+          <t>331035</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>387165</t>
+          <t>388812</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,06%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36093</t>
+          <t>34648</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60465</t>
+          <t>60503</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42081</t>
+          <t>41535</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63912</t>
+          <t>63634</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83342</t>
+          <t>83852</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116419</t>
+          <t>115904</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9462</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27536</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15360</t>
+          <t>15158</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34514</t>
+          <t>36051</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>403354</t>
+          <t>402705</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>736461</t>
+          <t>742497</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>221441</t>
+          <t>220575</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>287711</t>
+          <t>285390</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>653405</t>
+          <t>651038</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1143139</t>
+          <t>1123491</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>70,36%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>111481</t>
+          <t>98800</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>343139</t>
+          <t>341791</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>314492</t>
+          <t>316123</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>408010</t>
+          <t>398891</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>339036</t>
+          <t>358887</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>707419</t>
+          <t>705672</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,19%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38203</t>
+          <t>35889</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>131418</t>
+          <t>133199</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>75632</t>
+          <t>74030</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>112310</t>
+          <t>112366</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>107864</t>
+          <t>108022</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>223908</t>
+          <t>224551</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>19965</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19039</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14052</t>
+          <t>14319</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34643</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>199933</t>
+          <t>195825</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>243145</t>
+          <t>241877</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>168803</t>
+          <t>167630</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>201728</t>
+          <t>200428</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>376672</t>
+          <t>377699</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>430980</t>
+          <t>435468</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>207335</t>
+          <t>210171</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>253137</t>
+          <t>253459</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>214604</t>
+          <t>215002</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>246539</t>
+          <t>250764</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>432880</t>
+          <t>433486</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>489841</t>
+          <t>490237</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,44%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78934</t>
+          <t>77458</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>109952</t>
+          <t>110524</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>99030</t>
+          <t>98117</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>127304</t>
+          <t>124929</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>185264</t>
+          <t>183647</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>228182</t>
+          <t>225445</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>8288</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21642</t>
+          <t>21044</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13567</t>
+          <t>13432</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>26287</t>
+          <t>26333</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>25196</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>43178</t>
+          <t>43612</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>133336</t>
+          <t>132950</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>162289</t>
+          <t>163593</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>200922</t>
+          <t>201490</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>499308</t>
+          <t>495297</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>352859</t>
+          <t>355514</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>728120</t>
+          <t>729938</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>141713</t>
+          <t>141050</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>171054</t>
+          <t>171955</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>67563</t>
+          <t>71322</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>257156</t>
+          <t>260370</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>157245</t>
+          <t>163133</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>421032</t>
+          <t>415955</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>42005</t>
+          <t>42680</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>63076</t>
+          <t>63669</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>32884</t>
+          <t>36515</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>135179</t>
+          <t>133337</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>73411</t>
+          <t>67667</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>181651</t>
+          <t>182452</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13589</t>
+          <t>13886</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>28657</t>
+          <t>29520</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>74125</t>
+          <t>76104</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>98632</t>
+          <t>100053</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>83072</t>
+          <t>83096</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>107908</t>
+          <t>108019</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>165305</t>
+          <t>162952</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>198519</t>
+          <t>200221</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>108217</t>
+          <t>107748</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>134923</t>
+          <t>133439</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>164749</t>
+          <t>164301</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>193120</t>
+          <t>193236</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>280940</t>
+          <t>279128</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>318799</t>
+          <t>319239</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>48245</t>
+          <t>50334</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>69978</t>
+          <t>71522</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>114895</t>
+          <t>112886</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>139823</t>
+          <t>139508</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>170227</t>
+          <t>170484</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>202680</t>
+          <t>205086</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>17393</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>27751</t>
+          <t>27898</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24231</t>
+          <t>24788</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>39574</t>
+          <t>40225</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1680746</t>
+          <t>1679159</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2203223</t>
+          <t>2173471</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1465798</t>
+          <t>1467580</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2018492</t>
+          <t>2037453</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3188875</t>
+          <t>3194979</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3900777</t>
+          <t>3926612</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>877855</t>
+          <t>907561</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1267016</t>
+          <t>1271478</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1161807</t>
+          <t>1160249</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1552222</t>
+          <t>1560092</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2269600</t>
+          <t>2268320</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2790536</t>
+          <t>2792173</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>296365</t>
+          <t>303709</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>432440</t>
+          <t>430218</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>433337</t>
+          <t>429833</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>581781</t>
+          <t>585367</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>790006</t>
+          <t>794288</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>992459</t>
+          <t>993940</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>55565</t>
+          <t>54502</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>95790</t>
+          <t>95683</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>60668</t>
+          <t>60968</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>90459</t>
+          <t>93158</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>126868</t>
+          <t>126612</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>177960</t>
+          <t>178790</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P57B2_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>287989</t>
+          <t>287560</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>255176</t>
+          <t>257132</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>320033</t>
+          <t>316497</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>198438</t>
+          <t>228008</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>174788</t>
+          <t>199210</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>219323</t>
+          <t>251361</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>486428</t>
+          <t>515568</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>446271</t>
+          <t>476498</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>523631</t>
+          <t>554708</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>72,01%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>92070</t>
+          <t>101193</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64606</t>
+          <t>73182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>122164</t>
+          <t>130681</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>81229</t>
+          <t>92819</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63761</t>
+          <t>73666</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105079</t>
+          <t>118770</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>173299</t>
+          <t>194012</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139732</t>
+          <t>156010</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>212229</t>
+          <t>228414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13619</t>
+          <t>13051</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28865</t>
+          <t>30995</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33533</t>
+          <t>41685</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21396</t>
+          <t>27046</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50531</t>
+          <t>62436</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>47152</t>
+          <t>54735</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32042</t>
+          <t>35245</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70228</t>
+          <t>75217</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24633</t>
+          <t>21518</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25889</t>
+          <t>20694</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>234457</t>
+          <t>264652</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>206499</t>
+          <t>235369</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>260696</t>
+          <t>291077</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>239430</t>
+          <t>267791</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>140680</t>
+          <t>247002</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>285865</t>
+          <t>292457</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>473887</t>
+          <t>532442</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>346860</t>
+          <t>495495</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>526809</t>
+          <t>571073</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>58,39%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>150455</t>
+          <t>167363</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>126086</t>
+          <t>141313</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>176492</t>
+          <t>195791</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>236842</t>
+          <t>189434</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>186484</t>
+          <t>165777</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>345197</t>
+          <t>210458</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>387298</t>
+          <t>356797</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>331559</t>
+          <t>317476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>525925</t>
+          <t>389851</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>31667</t>
+          <t>37306</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20498</t>
+          <t>23614</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47726</t>
+          <t>53624</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30070</t>
+          <t>38626</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>27451</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42894</t>
+          <t>52634</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>61736</t>
+          <t>75932</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42753</t>
+          <t>57195</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80999</t>
+          <t>95190</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15173</t>
+          <t>15032</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1690</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13456</t>
+          <t>12719</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,22 +1703,22 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21404</t>
+          <t>22815</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>304595</t>
+          <t>347428</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>280077</t>
+          <t>319141</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>327588</t>
+          <t>372168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>292732</t>
+          <t>330869</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>273877</t>
+          <t>310152</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>310814</t>
+          <t>350488</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>597327</t>
+          <t>678296</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>564822</t>
+          <t>642417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>625996</t>
+          <t>714148</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,49%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>168728</t>
+          <t>196905</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>148094</t>
+          <t>172689</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>191222</t>
+          <t>223310</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>190710</t>
+          <t>222157</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>174197</t>
+          <t>204418</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>209440</t>
+          <t>244793</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>359438</t>
+          <t>419063</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>331035</t>
+          <t>386789</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>388812</t>
+          <t>453396</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,5%</t>
         </is>
       </c>
     </row>
@@ -2089,102 +2089,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>46320</t>
+          <t>58122</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34648</t>
+          <t>44803</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60503</t>
+          <t>74758</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>12,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>61733</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>50142</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>74642</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>9,93%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>8,07%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>12,01%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>119855</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>101959</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>140161</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>9,65%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>8,21%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>11,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>51985</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>41535</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>63634</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>11,74%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>98305</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>83852</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>115904</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>9,12%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>7,78%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>18382</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>11124</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>30789</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11932</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>23079</t>
+          <t>25082</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>16246</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36051</t>
+          <t>36182</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>541810</t>
+          <t>621460</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>541810</t>
+          <t>621460</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>541810</t>
+          <t>621460</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1078149</t>
+          <t>1242296</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1078149</t>
+          <t>1242296</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1078149</t>
+          <t>1242296</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>546956</t>
+          <t>323881</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>402705</t>
+          <t>296767</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>742497</t>
+          <t>352180</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>262149</t>
+          <t>288205</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>220575</t>
+          <t>265224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>285390</t>
+          <t>308415</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>809104</t>
+          <t>612086</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>651038</t>
+          <t>578746</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1123491</t>
+          <t>647619</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>45,2%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>238577</t>
+          <t>264259</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>98800</t>
+          <t>237371</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>341791</t>
+          <t>290779</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>343563</t>
+          <t>336822</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>316123</t>
+          <t>314083</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>398891</t>
+          <t>357352</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>582140</t>
+          <t>601081</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>358887</t>
+          <t>567537</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>705672</t>
+          <t>635670</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>88904</t>
+          <t>98811</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35889</t>
+          <t>82430</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>133199</t>
+          <t>118081</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>92564</t>
+          <t>95084</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>74030</t>
+          <t>80775</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>112366</t>
+          <t>111462</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>181467</t>
+          <t>193895</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>108022</t>
+          <t>173714</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>224551</t>
+          <t>220065</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10574</t>
+          <t>10562</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19965</t>
+          <t>17788</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13515</t>
+          <t>15119</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20055</t>
+          <t>22399</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>24089</t>
+          <t>25681</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>18044</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>36643</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>885010</t>
+          <t>697513</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>885010</t>
+          <t>697513</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>885010</t>
+          <t>697513</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>711791</t>
+          <t>735230</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>711791</t>
+          <t>735230</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>711791</t>
+          <t>735230</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1596800</t>
+          <t>1432743</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1596800</t>
+          <t>1432743</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1596800</t>
+          <t>1432743</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>219113</t>
+          <t>239955</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>195825</t>
+          <t>218716</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>241877</t>
+          <t>263243</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>184114</t>
+          <t>207227</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>167630</t>
+          <t>189145</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>200428</t>
+          <t>224374</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>403227</t>
+          <t>447182</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>377699</t>
+          <t>418448</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>435468</t>
+          <t>479228</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,56%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>231495</t>
+          <t>250659</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>210171</t>
+          <t>227165</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>253459</t>
+          <t>272195</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>230817</t>
+          <t>255304</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>215002</t>
+          <t>237926</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>250764</t>
+          <t>273833</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>462312</t>
+          <t>505963</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>433486</t>
+          <t>476010</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>490237</t>
+          <t>535374</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,19%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>92956</t>
+          <t>99277</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77458</t>
+          <t>82650</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>110524</t>
+          <t>118685</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>111520</t>
+          <t>122651</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>98117</t>
+          <t>108615</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>124929</t>
+          <t>139566</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>204475</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>183647</t>
+          <t>198831</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>225445</t>
+          <t>243894</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>13642</t>
+          <t>14906</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21044</t>
+          <t>23264</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19440</t>
+          <t>21569</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13432</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>26333</t>
+          <t>29743</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>33082</t>
+          <t>36475</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>25196</t>
+          <t>26908</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>43612</t>
+          <t>46143</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>557206</t>
+          <t>604796</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>557206</t>
+          <t>604796</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>557206</t>
+          <t>604796</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>545891</t>
+          <t>606751</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>545891</t>
+          <t>606751</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>545891</t>
+          <t>606751</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1103096</t>
+          <t>1211547</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1103096</t>
+          <t>1211547</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1103096</t>
+          <t>1211547</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>148556</t>
+          <t>165044</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>132950</t>
+          <t>149293</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>163593</t>
+          <t>181465</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>341926</t>
+          <t>149034</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>134929</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>495297</t>
+          <t>164200</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>490482</t>
+          <t>314079</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>355514</t>
+          <t>291780</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>729938</t>
+          <t>335895</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>156866</t>
+          <t>173811</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>141050</t>
+          <t>155826</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>171955</t>
+          <t>189762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>167364</t>
+          <t>182662</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>71322</t>
+          <t>168188</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>260370</t>
+          <t>197692</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>324230</t>
+          <t>356474</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>163133</t>
+          <t>333827</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>415955</t>
+          <t>379410</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>45,09%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>52015</t>
+          <t>56838</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>42680</t>
+          <t>45569</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>63669</t>
+          <t>68495</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>85406</t>
+          <t>92920</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>36515</t>
+          <t>79810</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>133337</t>
+          <t>104359</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>137421</t>
+          <t>149758</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>67667</t>
+          <t>133114</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>182452</t>
+          <t>165944</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8815</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13886</t>
+          <t>14533</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>12414</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>18253</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>20005</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>9601</t>
+          <t>15383</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>29520</t>
+          <t>30017</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>365806</t>
+          <t>404508</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>365806</t>
+          <t>404508</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>365806</t>
+          <t>404508</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>606332</t>
+          <t>437031</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>606332</t>
+          <t>437031</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>606332</t>
+          <t>437031</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>972138</t>
+          <t>841540</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>972138</t>
+          <t>841540</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>972138</t>
+          <t>841540</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>87145</t>
+          <t>94381</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>76104</t>
+          <t>81887</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>100053</t>
+          <t>108124</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>94898</t>
+          <t>105222</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>83096</t>
+          <t>91343</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>108019</t>
+          <t>119045</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>182043</t>
+          <t>199603</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>162952</t>
+          <t>181011</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>200221</t>
+          <t>219900</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>120567</t>
+          <t>134689</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>107748</t>
+          <t>119823</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>133439</t>
+          <t>149346</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>178651</t>
+          <t>194286</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>164301</t>
+          <t>179229</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>193236</t>
+          <t>210159</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>299218</t>
+          <t>328974</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>279128</t>
+          <t>305789</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>319239</t>
+          <t>349937</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,74%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>59346</t>
+          <t>64204</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>50334</t>
+          <t>53765</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>71522</t>
+          <t>76948</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>126938</t>
+          <t>137529</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>112886</t>
+          <t>123953</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>139508</t>
+          <t>152431</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>186284</t>
+          <t>201733</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>170484</t>
+          <t>181974</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>205086</t>
+          <t>220797</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>11153</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>17393</t>
+          <t>17762</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>20921</t>
+          <t>22840</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>15313</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>27898</t>
+          <t>30169</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>32074</t>
+          <t>34778</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24788</t>
+          <t>26832</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>40225</t>
+          <t>43713</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>278211</t>
+          <t>305212</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>278211</t>
+          <t>305212</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>278211</t>
+          <t>305212</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>421408</t>
+          <t>459876</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>421408</t>
+          <t>459876</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>421408</t>
+          <t>459876</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>699619</t>
+          <t>765088</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>699619</t>
+          <t>765088</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>699619</t>
+          <t>765088</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1828811</t>
+          <t>1722901</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1679159</t>
+          <t>1650404</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2173471</t>
+          <t>1789014</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1613686</t>
+          <t>1576356</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1467580</t>
+          <t>1523413</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>2037453</t>
+          <t>1639012</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>3442497</t>
+          <t>3299257</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3194979</t>
+          <t>3211076</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3926612</t>
+          <t>3385745</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>46,75%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>1158759</t>
+          <t>1288878</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>907561</t>
+          <t>1231686</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1271478</t>
+          <t>1355857</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1429176</t>
+          <t>1473485</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1160249</t>
+          <t>1415883</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1560092</t>
+          <t>1525100</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2587934</t>
+          <t>2762363</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2268320</t>
+          <t>2680085</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2792173</t>
+          <t>2842346</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>384827</t>
+          <t>427608</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>303709</t>
+          <t>390934</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>430218</t>
+          <t>469130</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>532014</t>
+          <t>590228</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>429833</t>
+          <t>555382</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>585367</t>
+          <t>631569</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>916841</t>
+          <t>1017836</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>794288</t>
+          <t>969029</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>993940</t>
+          <t>1071633</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>73709</t>
+          <t>78161</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>54502</t>
+          <t>59741</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>95683</t>
+          <t>96405</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>77060</t>
+          <t>83875</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>60968</t>
+          <t>68427</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>93158</t>
+          <t>99560</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>150768</t>
+          <t>162036</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>126612</t>
+          <t>140982</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>178790</t>
+          <t>185781</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3446105</t>
+          <t>3517549</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3446105</t>
+          <t>3517549</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3446105</t>
+          <t>3517549</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3651936</t>
+          <t>3723944</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3651936</t>
+          <t>3723944</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3651936</t>
+          <t>3723944</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7098041</t>
+          <t>7241493</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7098041</t>
+          <t>7241493</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7098041</t>
+          <t>7241493</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
